--- a/06_modelo_demanda/Modelo_demanda_oferta_IoT_LosRios.xlsx
+++ b/06_modelo_demanda/Modelo_demanda_oferta_IoT_LosRios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\Ingenier-a-en-Internet-of-Things\06_modelo_demanda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F4649D-DF4C-40BA-909C-9B8268F76B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD68DC8-F8A7-4E71-A8DE-04E1C3BED954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,13 @@
     <sheet name="Léame" sheetId="1" r:id="rId1"/>
     <sheet name="SRI_LosRios" sheetId="2" r:id="rId2"/>
     <sheet name="INEC_LosRios" sheetId="3" r:id="rId3"/>
-    <sheet name="Supuestos" sheetId="4" r:id="rId4"/>
-    <sheet name="Demanda" sheetId="5" r:id="rId5"/>
-    <sheet name="Oferta" sheetId="6" r:id="rId6"/>
-    <sheet name="Brecha" sheetId="7" r:id="rId7"/>
-    <sheet name="Sensibilidad" sheetId="8" r:id="rId8"/>
+    <sheet name="SENESCYT_TIC" sheetId="4" r:id="rId4"/>
+    <sheet name="Supuestos" sheetId="5" r:id="rId5"/>
+    <sheet name="Demanda" sheetId="6" r:id="rId6"/>
+    <sheet name="Oferta" sheetId="7" r:id="rId7"/>
+    <sheet name="Brecha" sheetId="8" r:id="rId8"/>
+    <sheet name="Sensibilidad" sheetId="9" r:id="rId9"/>
+    <sheet name="Muestra" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="211">
   <si>
     <t>Modelo de demanda y oferta de profesionales IoT en Los Ríos</t>
   </si>
@@ -69,7 +71,7 @@
     <t>Hojas</t>
   </si>
   <si>
-    <t>SRI_LosRios y INEC_LosRios: datos observados. Supuestos: entradas. Demanda, Oferta, Brecha y Sensibilidad: cálculos.</t>
+    <t>SRI_LosRios, INEC_LosRios y SENESCYT_TIC: datos observados. Supuestos: entradas. Demanda, Oferta, Brecha y Sensibilidad: cálculos.</t>
   </si>
   <si>
     <t>Horizonte</t>
@@ -81,13 +83,13 @@
     <t>Fuentes</t>
   </si>
   <si>
-    <t>SRI: catastro RUC de Los Ríos (datos abiertos, actualizado el 1-IX-2026). INEC: Registro Estadístico de Empresas 2025, ENEMDU anual 2025, Censo 2022. SENESCYT: graduados TIC 2020 y 2021 tomados de la Política de Transformación Digital 2025-2030 (MINTEL). UTEQ: informe de rendición de cuentas 2024.</t>
+    <t>SRI: catastro RUC de Los Ríos (datos abiertos, actualizado el 1-IX-2026). INEC: Registro Estadístico de Empresas 2025, ENEMDU anual 2025, Censo 2022. SENESCYT: tableros de matrícula UEP y de títulos nacionales, y graduados TIC 2020 y 2021 de la Política de Transformación Digital 2025-2030 (MINTEL). UTEQ: informe de rendición de cuentas 2024.</t>
   </si>
   <si>
     <t>Límites de los datos</t>
   </si>
   <si>
-    <t>El catastro RUC no trae tamaño de empresa; se usa "sociedad o persona natural obligada a llevar contabilidad" como aproximación de empresa formal. No se obtuvo de la SENESCYT la serie de graduados TIC por provincia (el servidor de sus datos abiertos no respondió); la oferta se estima con proxies que se detallan en la hoja Oferta.</t>
+    <t>El catastro RUC no trae tamaño de empresa; se usa "sociedad o persona natural obligada a llevar contabilidad" como aproximación de empresa formal. La matrícula y los títulos TIC de la SENESCYT se leyeron de sus tableros públicos (la base de datos abiertos no estaba disponible). La serie de títulos TIC por provincia y año no se pudo extraer completa: se usa 2024 y el acumulado; la oferta de graduados se estima a partir de la matrícula.</t>
   </si>
   <si>
     <t>Privacidad</t>
@@ -288,6 +290,63 @@
     <t>INEC, Censo 2022 (Los Ríos, cuarta provincia más poblada)</t>
   </si>
   <si>
+    <t>Matrícula y títulos TIC (SENESCYT)</t>
+  </si>
+  <si>
+    <t>Fuente: tableros públicos de la SENESCYT (Registro de matrícula UEP y Títulos nacionales), consultados el 26-IX-2026. Campo de estudio "Tecnologías de la información y la comunicación".</t>
+  </si>
+  <si>
+    <t>Matrícula total UEP en Los Ríos</t>
+  </si>
+  <si>
+    <t>Matrícula TIC UEP en Los Ríos</t>
+  </si>
+  <si>
+    <t>% TIC</t>
+  </si>
+  <si>
+    <t>Antes de 2018 el tablero no registra matrícula en el campo TIC en Los Ríos (efecto de la clasificación por campos vigente).</t>
+  </si>
+  <si>
+    <t>Provincia</t>
+  </si>
+  <si>
+    <t>Matrícula UEP 2022</t>
+  </si>
+  <si>
+    <t>Matrícula TIC UEP 2022</t>
+  </si>
+  <si>
+    <t>% TIC 2022</t>
+  </si>
+  <si>
+    <t>Títulos registrados 2024, todos</t>
+  </si>
+  <si>
+    <t>Títulos TIC 2024, todos los niveles</t>
+  </si>
+  <si>
+    <t>Guayas</t>
+  </si>
+  <si>
+    <t>Bolívar</t>
+  </si>
+  <si>
+    <t>Santo Domingo de los Tsáchilas</t>
+  </si>
+  <si>
+    <t>Títulos TIC registrados entre 2013 y 2024 (acumulado, todos los niveles): Guayas 5.597; Los Ríos 518; Santo Domingo 319. Bolívar no aparece entre las 14 provincias con más títulos TIC.</t>
+  </si>
+  <si>
+    <t>Títulos nacionales, todos los campos</t>
+  </si>
+  <si>
+    <t>Títulos nacionales TIC</t>
+  </si>
+  <si>
+    <t>Cautela: los títulos TIC de años anteriores a 2022 están subregistrados por la clasificación por campos; la Política del MINTEL cita 7.476 graduados TIC en 2021 frente a 1.797 en este tablero.</t>
+  </si>
+  <si>
     <t>Supuestos del modelo (celdas amarillas: editables)</t>
   </si>
   <si>
@@ -363,16 +422,10 @@
     <t>4. Oferta de graduados TIC en Los Ríos</t>
   </si>
   <si>
-    <t>Graduados TIC en el país, 2021 (SENESCYT, vía MINTEL)</t>
-  </si>
-  <si>
-    <t>Graduados TIC en el país, 2020 (SENESCYT, vía MINTEL)</t>
-  </si>
-  <si>
-    <t>Población de Los Ríos sobre la nacional (proxy máximo)</t>
-  </si>
-  <si>
-    <t>Población nacional del Censo 2022 tomada como 16.938.986; verificar</t>
+    <t>Matrícula TIC en IES de Los Ríos, 2023 (SENESCYT)</t>
+  </si>
+  <si>
+    <t>Títulos TIC registrados en 2024 por IES de Los Ríos, todos los niveles (SENESCYT)</t>
   </si>
   <si>
     <t>Oferta baja</t>
@@ -387,7 +440,7 @@
     <t>Graduados TIC por año que salen de IES de Los Ríos</t>
   </si>
   <si>
-    <t>Baja: máximo identificado en las carreras TIC de la UTEQ en la cohorte 2018-2019 (45 a 69 graduados). Base: 2,5 % del total nacional. Alta: participación de la población de Los Ríos (5,3 %).</t>
+    <t>Baja: títulos TIC registrados en 2024. Base: matrícula TIC 2023 entre la duración media de la carrera, por la tasa de titulación. Alta: matrícula TIC 2023 entre la duración media, si todos se titularan.</t>
   </si>
   <si>
     <t>% de esos graduados con competencias útiles para IoT</t>
@@ -583,6 +636,45 @@
   </si>
   <si>
     <t>Lectura: la fila 1,00x y la columna 1,5 reproducen el escenario base. Compare con los graduados por año de la hoja Brecha.</t>
+  </si>
+  <si>
+    <t>Marco muestral y asignación de la encuesta a empleadores</t>
+  </si>
+  <si>
+    <t>Marco: empresas formales de los grupos G1 a G9 del catastro RUC del SRI. Asignación proporcional por grupo con un mínimo por estrato.</t>
+  </si>
+  <si>
+    <t>Población N (empresas formales G1 a G9)</t>
+  </si>
+  <si>
+    <t>Nivel de confianza (z)</t>
+  </si>
+  <si>
+    <t>Error máximo (e)</t>
+  </si>
+  <si>
+    <t>Proporción esperada (p)</t>
+  </si>
+  <si>
+    <t>Tamaño de muestra n</t>
+  </si>
+  <si>
+    <t>Mínimo por estrato</t>
+  </si>
+  <si>
+    <t>Grupo (estrato)</t>
+  </si>
+  <si>
+    <t>Empresas formales Nh</t>
+  </si>
+  <si>
+    <t>Muestra proporcional</t>
+  </si>
+  <si>
+    <t>Muestra con mínimo</t>
+  </si>
+  <si>
+    <t>Los estratos pequeños se encuestan casi completos (censo) por el mínimo; por eso el total con mínimo supera a n. Se recomienda además estratificar por cantón con las cifras de la hoja SRI_LosRios.</t>
   </si>
 </sst>
 </file>
@@ -683,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -714,6 +806,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -819,7 +912,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3C09-4FBB-A061-5F090520D062}"/>
+              <c16:uniqueId val="{00000000-F558-4161-A057-99F331B91AFB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -867,20 +960,20 @@
                 <c:formatCode>#,##0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>9.35</c:v>
+                  <c:v>7.8000000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.35</c:v>
+                  <c:v>7.8000000000000007</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.35</c:v>
+                  <c:v>7.8000000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3C09-4FBB-A061-5F090520D062}"/>
+              <c16:uniqueId val="{00000001-F558-4161-A057-99F331B91AFB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -941,7 +1034,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3C09-4FBB-A061-5F090520D062}"/>
+              <c16:uniqueId val="{00000002-F558-4161-A057-99F331B91AFB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1040,7 +1133,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1432,6 +1525,278 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="7">
+        <f>SRI_LosRios!D5+SRI_LosRios!D6+SRI_LosRios!D7+SRI_LosRios!D8+SRI_LosRios!D9+SRI_LosRios!D10+SRI_LosRios!D11+SRI_LosRios!D12+SRI_LosRios!D13</f>
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="24">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="9">
+        <f>ROUNDUP(B4*B5^2*B7*(1-B7)/(B6^2*(B4-1)+B5^2*B7*(1-B7)),0)</f>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="str">
+        <f>SRI_LosRios!A5</f>
+        <v>G1 Agricultura, ganadería y silvicultura</v>
+      </c>
+      <c r="B12" s="7">
+        <f>SRI_LosRios!D5</f>
+        <v>1397</v>
+      </c>
+      <c r="C12" s="11">
+        <f t="shared" ref="C12:C20" si="0">$B$8*B12/$B$4</f>
+        <v>132.09238688702249</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" ref="D12:D20" si="1">MIN(B12,MAX($B$9,ROUND(C12,0)))</f>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="str">
+        <f>SRI_LosRios!A6</f>
+        <v>G2 Pesca y acuicultura</v>
+      </c>
+      <c r="B13" s="7">
+        <f>SRI_LosRios!D6</f>
+        <v>14</v>
+      </c>
+      <c r="C13" s="11">
+        <f t="shared" si="0"/>
+        <v>1.323760498509889</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="str">
+        <f>SRI_LosRios!A7</f>
+        <v>G3 Alimentos y bebidas (agroindustria)</v>
+      </c>
+      <c r="B14" s="7">
+        <f>SRI_LosRios!D7</f>
+        <v>93</v>
+      </c>
+      <c r="C14" s="11">
+        <f t="shared" si="0"/>
+        <v>8.7935518829585479</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="str">
+        <f>SRI_LosRios!A8</f>
+        <v>G4 Otras manufacturas</v>
+      </c>
+      <c r="B15" s="7">
+        <f>SRI_LosRios!D8</f>
+        <v>163</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="0"/>
+        <v>15.412354375507993</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="str">
+        <f>SRI_LosRios!A9</f>
+        <v>G5 Energía, agua y saneamiento</v>
+      </c>
+      <c r="B16" s="7">
+        <f>SRI_LosRios!D9</f>
+        <v>97</v>
+      </c>
+      <c r="C16" s="11">
+        <f t="shared" si="0"/>
+        <v>9.1717691682470868</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="str">
+        <f>SRI_LosRios!A10</f>
+        <v>G6 Transporte y almacenamiento</v>
+      </c>
+      <c r="B17" s="7">
+        <f>SRI_LosRios!D10</f>
+        <v>507</v>
+      </c>
+      <c r="C17" s="11">
+        <f t="shared" si="0"/>
+        <v>47.939040910322404</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="str">
+        <f>SRI_LosRios!A11</f>
+        <v>G7 Comercio al por mayor</v>
+      </c>
+      <c r="B18" s="7">
+        <f>SRI_LosRios!D11</f>
+        <v>1067</v>
+      </c>
+      <c r="C18" s="11">
+        <f t="shared" si="0"/>
+        <v>100.88946085071797</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="str">
+        <f>SRI_LosRios!A12</f>
+        <v>G8 Administración pública (GAD y entidades)</v>
+      </c>
+      <c r="B19" s="7">
+        <f>SRI_LosRios!D12</f>
+        <v>96</v>
+      </c>
+      <c r="C19" s="11">
+        <f t="shared" si="0"/>
+        <v>9.077214846924953</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="str">
+        <f>SRI_LosRios!A13</f>
+        <v>G9 Proveedores tecnológicos (TIC, ingeniería, I+D)</v>
+      </c>
+      <c r="B20" s="7">
+        <f>SRI_LosRios!D13</f>
+        <v>257</v>
+      </c>
+      <c r="C20" s="11">
+        <f t="shared" si="0"/>
+        <v>24.300460579788677</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="9">
+        <f>SUM(B12:B20)</f>
+        <v>3691</v>
+      </c>
+      <c r="C21" s="18">
+        <f>SUM(C12:C20)</f>
+        <v>349</v>
+      </c>
+      <c r="D21" s="9">
+        <f>SUM(D12:D20)</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E53"/>
@@ -2095,7 +2460,450 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>2016</v>
+      </c>
+      <c r="B5" s="7">
+        <v>16655</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12">
+        <f t="shared" ref="D5:D12" si="0">C5/B5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="7">
+        <v>18660</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>2018</v>
+      </c>
+      <c r="B7" s="7">
+        <v>20885</v>
+      </c>
+      <c r="C7" s="7">
+        <v>346</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" si="0"/>
+        <v>1.6566914053148193E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>2019</v>
+      </c>
+      <c r="B8" s="7">
+        <v>21207</v>
+      </c>
+      <c r="C8" s="7">
+        <v>559</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" si="0"/>
+        <v>2.6359221011930022E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>2020</v>
+      </c>
+      <c r="B9" s="7">
+        <v>23580</v>
+      </c>
+      <c r="C9" s="7">
+        <v>760</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="0"/>
+        <v>3.2230703986429174E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2021</v>
+      </c>
+      <c r="B10" s="7">
+        <v>25581</v>
+      </c>
+      <c r="C10" s="7">
+        <v>942</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>3.6824205464993549E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B11" s="7">
+        <v>26653</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1005</v>
+      </c>
+      <c r="D11" s="12">
+        <f t="shared" si="0"/>
+        <v>3.7706824747683186E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B12" s="7">
+        <v>27624</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1021</v>
+      </c>
+      <c r="D12" s="12">
+        <f t="shared" si="0"/>
+        <v>3.6960613958876343E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="7">
+        <v>26653</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1005</v>
+      </c>
+      <c r="D18" s="12">
+        <f>C18/B18</f>
+        <v>3.7706824747683186E-2</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3205</v>
+      </c>
+      <c r="F18" s="7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="7">
+        <v>207192</v>
+      </c>
+      <c r="C19" s="7">
+        <v>9708</v>
+      </c>
+      <c r="D19" s="12">
+        <f>C19/B19</f>
+        <v>4.6855090930151742E-2</v>
+      </c>
+      <c r="E19" s="7">
+        <v>38212</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="7">
+        <v>7529</v>
+      </c>
+      <c r="C20" s="7">
+        <v>183</v>
+      </c>
+      <c r="D20" s="12">
+        <f>C20/B20</f>
+        <v>2.430601673529021E-2</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1265</v>
+      </c>
+      <c r="F20" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6752</v>
+      </c>
+      <c r="C21" s="7">
+        <v>389</v>
+      </c>
+      <c r="D21" s="12">
+        <f>C21/B21</f>
+        <v>5.7612559241706163E-2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1438</v>
+      </c>
+      <c r="F21" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="7">
+        <v>792530</v>
+      </c>
+      <c r="C22" s="7">
+        <v>33220</v>
+      </c>
+      <c r="D22" s="12">
+        <f>C22/B22</f>
+        <v>4.1916394332075758E-2</v>
+      </c>
+      <c r="E22" s="7">
+        <v>123378</v>
+      </c>
+      <c r="F22" s="7">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>2013</v>
+      </c>
+      <c r="B27" s="7">
+        <v>107971</v>
+      </c>
+      <c r="C27" s="7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>2014</v>
+      </c>
+      <c r="B28" s="7">
+        <v>100161</v>
+      </c>
+      <c r="C28" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>2015</v>
+      </c>
+      <c r="B29" s="7">
+        <v>145723</v>
+      </c>
+      <c r="C29" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>2016</v>
+      </c>
+      <c r="B30" s="7">
+        <v>152544</v>
+      </c>
+      <c r="C30" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <v>2017</v>
+      </c>
+      <c r="B31" s="7">
+        <v>130748</v>
+      </c>
+      <c r="C31" s="7">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <v>2018</v>
+      </c>
+      <c r="B32" s="7">
+        <v>114504</v>
+      </c>
+      <c r="C32" s="7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <v>2019</v>
+      </c>
+      <c r="B33" s="7">
+        <v>109933</v>
+      </c>
+      <c r="C33" s="7">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>2020</v>
+      </c>
+      <c r="B34" s="7">
+        <v>101048</v>
+      </c>
+      <c r="C34" s="7">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <v>2021</v>
+      </c>
+      <c r="B35" s="7">
+        <v>151518</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B36" s="7">
+        <v>186946</v>
+      </c>
+      <c r="C36" s="7">
+        <v>4093</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B37" s="7">
+        <v>208299</v>
+      </c>
+      <c r="C37" s="7">
+        <v>7663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B38" s="7">
+        <v>123378</v>
+      </c>
+      <c r="C38" s="7">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="78" customWidth="1"/>
@@ -2104,22 +2912,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="B5" s="7">
         <f>INEC_LosRios!B6</f>
@@ -2128,7 +2936,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="B6" s="7">
         <f>SRI_LosRios!D17-SRI_LosRios!D20</f>
@@ -2137,19 +2945,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B7" s="12">
         <f>B5/B6</f>
         <v>0.30087142638740255</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B8" s="13">
         <f>ROUND(B7,2)</f>
@@ -2158,7 +2966,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B9" s="13">
         <v>1</v>
@@ -2166,30 +2974,30 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2401,29 +3209,29 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B26" s="14">
         <v>1</v>
@@ -2437,7 +3245,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B27" s="15">
         <v>0</v>
@@ -2445,118 +3253,109 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B30" s="7">
-        <v>7476</v>
+        <f>SENESCYT_TIC!C12</f>
+        <v>1021</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B31" s="7">
-        <v>5079</v>
+        <f>SENESCYT_TIC!F18</f>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B32" s="12">
-        <f>INEC_LosRios!B11/16938986</f>
-        <v>5.3052290142987304E-2</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>110</v>
+      <c r="A32" s="5"/>
+      <c r="B32" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>113</v>
+      <c r="A33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="7">
+        <f>B31</f>
+        <v>69</v>
+      </c>
+      <c r="C33" s="15">
+        <f>ROUND(B30/B41*B39,0)</f>
+        <v>156</v>
+      </c>
+      <c r="D33" s="15">
+        <f>ROUND(B30/B41,0)</f>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="15">
-        <v>69</v>
-      </c>
-      <c r="C34" s="15">
-        <f>ROUND(B30*0.025,0)</f>
-        <v>187</v>
-      </c>
-      <c r="D34" s="15">
-        <f>ROUND(B30*B32,0)</f>
-        <v>397</v>
+      <c r="A34" s="10" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" s="13">
+      <c r="A35" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="13">
         <v>0.02</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C35" s="13">
         <v>0.05</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D35" s="13">
         <v>0.1</v>
       </c>
     </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>117</v>
+      <c r="A38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="15">
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="15">
-        <v>40</v>
+        <v>136</v>
+      </c>
+      <c r="B39" s="13">
+        <v>0.60960000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="13">
-        <v>0.60960000000000003</v>
+        <v>137</v>
+      </c>
+      <c r="B40" s="16">
+        <v>2027</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B41" s="16">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" s="16">
         <v>4</v>
       </c>
     </row>
@@ -2565,8 +3364,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2578,44 +3377,44 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2998,7 +3797,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B14" s="18">
         <f>SUM(B5:B13)</f>
@@ -3035,26 +3834,26 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B18" s="7">
         <f>E14*Supuestos!B26-Supuestos!$B$27</f>
@@ -3071,7 +3870,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B19" s="7">
         <f>G14*Supuestos!C26-Supuestos!$B$27</f>
@@ -3088,7 +3887,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B20" s="7">
         <f>I14*Supuestos!D26-Supuestos!$B$27</f>
@@ -3105,18 +3904,18 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -3250,8 +4049,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3261,65 +4060,65 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B5" s="7">
-        <f>Supuestos!B34</f>
+        <f>Supuestos!B33</f>
         <v>69</v>
       </c>
       <c r="C5" s="7">
-        <f>Supuestos!C34</f>
-        <v>187</v>
+        <f>Supuestos!C33</f>
+        <v>156</v>
       </c>
       <c r="D5" s="7">
-        <f>Supuestos!D34</f>
-        <v>397</v>
+        <f>Supuestos!D33</f>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B6" s="12">
-        <f>Supuestos!B36</f>
+        <f>Supuestos!B35</f>
         <v>0.02</v>
       </c>
       <c r="C6" s="12">
-        <f>Supuestos!C36</f>
+        <f>Supuestos!C35</f>
         <v>0.05</v>
       </c>
       <c r="D6" s="12">
-        <f>Supuestos!D36</f>
+        <f>Supuestos!D35</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B7" s="18">
         <f>B5*B6</f>
@@ -3327,35 +4126,35 @@
       </c>
       <c r="C7" s="18">
         <f>C5*C6</f>
-        <v>9.35</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="D7" s="18">
         <f>D5*D6</f>
-        <v>39.700000000000003</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B11" s="11">
         <f>B7*4</f>
@@ -3363,16 +4162,16 @@
       </c>
       <c r="C11" s="11">
         <f>C7*4</f>
-        <v>37.4</v>
+        <v>31.200000000000003</v>
       </c>
       <c r="D11" s="11">
         <f>D7*4</f>
-        <v>158.80000000000001</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="B12" s="11">
         <f>B7*5</f>
@@ -3380,47 +4179,47 @@
       </c>
       <c r="C12" s="11">
         <f>C7*5</f>
-        <v>46.75</v>
+        <v>39</v>
       </c>
       <c r="D12" s="11">
         <f>D7*5</f>
-        <v>198.5</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B16" s="19">
-        <f>Supuestos!B41+Supuestos!B42</f>
+        <f>Supuestos!B40+Supuestos!B41</f>
         <v>2031</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B17" s="11">
-        <f>Supuestos!B39*Supuestos!B40</f>
+        <f>Supuestos!B38*Supuestos!B39</f>
         <v>24.384</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B18" s="11">
         <f>MAX(0,2030-B16+1)*B17</f>
@@ -3429,7 +4228,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B19" s="11">
         <f>MAX(0,2031-B16+1)*B17</f>
@@ -3438,7 +4237,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B20" s="11">
         <f>B17</f>
@@ -3450,8 +4249,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3464,41 +4263,41 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B7" s="21">
         <f>Demanda!B18-Oferta!B11</f>
@@ -3506,16 +4305,16 @@
       </c>
       <c r="C7" s="21">
         <f>Demanda!B18-Oferta!C11</f>
-        <v>-2.5114999999999981</v>
+        <v>3.6884999999999977</v>
       </c>
       <c r="D7" s="21">
         <f>Demanda!B18-Oferta!D11</f>
-        <v>-123.91150000000002</v>
+        <v>-67.111500000000007</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B8" s="21">
         <f>Demanda!B19-Oferta!B11</f>
@@ -3523,16 +4322,16 @@
       </c>
       <c r="C8" s="21">
         <f>Demanda!B19-Oferta!C11</f>
-        <v>82.353999999999985</v>
+        <v>88.553999999999988</v>
       </c>
       <c r="D8" s="21">
         <f>Demanda!B19-Oferta!D11</f>
-        <v>-39.046000000000021</v>
+        <v>17.753999999999991</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B9" s="21">
         <f>Demanda!B20-Oferta!B11</f>
@@ -3540,35 +4339,35 @@
       </c>
       <c r="C9" s="21">
         <f>Demanda!B20-Oferta!C11</f>
-        <v>245.23</v>
+        <v>251.43</v>
       </c>
       <c r="D9" s="21">
         <f>Demanda!B20-Oferta!D11</f>
-        <v>123.82999999999998</v>
+        <v>180.63</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B13" s="21">
         <f>Demanda!B18-Oferta!B11-Oferta!B18</f>
@@ -3576,16 +4375,16 @@
       </c>
       <c r="C13" s="21">
         <f>Demanda!B18-Oferta!C11-Oferta!B18</f>
-        <v>-2.5114999999999981</v>
+        <v>3.6884999999999977</v>
       </c>
       <c r="D13" s="21">
         <f>Demanda!B18-Oferta!D11-Oferta!B18</f>
-        <v>-123.91150000000002</v>
+        <v>-67.111500000000007</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B14" s="21">
         <f>Demanda!B19-Oferta!B11-Oferta!B18</f>
@@ -3593,16 +4392,16 @@
       </c>
       <c r="C14" s="21">
         <f>Demanda!B19-Oferta!C11-Oferta!B18</f>
-        <v>82.353999999999985</v>
+        <v>88.553999999999988</v>
       </c>
       <c r="D14" s="21">
         <f>Demanda!B19-Oferta!D11-Oferta!B18</f>
-        <v>-39.046000000000021</v>
+        <v>17.753999999999991</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B15" s="21">
         <f>Demanda!B20-Oferta!B11-Oferta!B18</f>
@@ -3610,40 +4409,40 @@
       </c>
       <c r="C15" s="21">
         <f>Demanda!B20-Oferta!C11-Oferta!B18</f>
-        <v>245.23</v>
+        <v>251.43</v>
       </c>
       <c r="D15" s="21">
         <f>Demanda!B20-Oferta!D11-Oferta!B18</f>
-        <v>123.82999999999998</v>
+        <v>180.63</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B21" s="21">
         <f>Demanda!C18-Oferta!B12</f>
@@ -3651,16 +4450,16 @@
       </c>
       <c r="C21" s="21">
         <f>Demanda!C18-Oferta!C12</f>
-        <v>2.8812499999999943</v>
+        <v>10.631249999999994</v>
       </c>
       <c r="D21" s="21">
         <f>Demanda!C18-Oferta!D12</f>
-        <v>-148.86875000000001</v>
+        <v>-77.868750000000006</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B22" s="21">
         <f>Demanda!C19-Oferta!B12</f>
@@ -3668,16 +4467,16 @@
       </c>
       <c r="C22" s="21">
         <f>Demanda!C19-Oferta!C12</f>
-        <v>117.96574999999999</v>
+        <v>125.71574999999999</v>
       </c>
       <c r="D22" s="21">
         <f>Demanda!C19-Oferta!D12</f>
-        <v>-33.784250000000014</v>
+        <v>37.215749999999986</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B23" s="21">
         <f>Demanda!C20-Oferta!B12</f>
@@ -3685,35 +4484,35 @@
       </c>
       <c r="C23" s="21">
         <f>Demanda!C20-Oferta!C12</f>
-        <v>327.5</v>
+        <v>335.25</v>
       </c>
       <c r="D23" s="21">
         <f>Demanda!C20-Oferta!D12</f>
-        <v>175.75</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B27" s="21">
         <f>Demanda!C18-Oferta!B12-Oferta!B19</f>
@@ -3721,16 +4520,16 @@
       </c>
       <c r="C27" s="21">
         <f>Demanda!C18-Oferta!C12-Oferta!B19</f>
-        <v>-21.502750000000006</v>
+        <v>-13.752750000000006</v>
       </c>
       <c r="D27" s="21">
         <f>Demanda!C18-Oferta!D12-Oferta!B19</f>
-        <v>-173.25274999999999</v>
+        <v>-102.25275000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B28" s="21">
         <f>Demanda!C19-Oferta!B12-Oferta!B19</f>
@@ -3738,16 +4537,16 @@
       </c>
       <c r="C28" s="21">
         <f>Demanda!C19-Oferta!C12-Oferta!B19</f>
-        <v>93.581749999999985</v>
+        <v>101.33174999999999</v>
       </c>
       <c r="D28" s="21">
         <f>Demanda!C19-Oferta!D12-Oferta!B19</f>
-        <v>-58.168250000000015</v>
+        <v>12.831749999999985</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B29" s="21">
         <f>Demanda!C20-Oferta!B12-Oferta!B19</f>
@@ -3755,41 +4554,41 @@
       </c>
       <c r="C29" s="21">
         <f>Demanda!C20-Oferta!C12-Oferta!B19</f>
-        <v>303.11599999999999</v>
+        <v>310.86599999999999</v>
       </c>
       <c r="D29" s="21">
         <f>Demanda!C20-Oferta!D12-Oferta!B19</f>
-        <v>151.36599999999999</v>
+        <v>222.36599999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B34" s="11">
         <f>Demanda!D18</f>
@@ -3797,7 +4596,7 @@
       </c>
       <c r="C34" s="11">
         <f>Oferta!C7</f>
-        <v>9.35</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="D34" s="11">
         <f>Oferta!B20</f>
@@ -3805,16 +4604,16 @@
       </c>
       <c r="E34" s="17">
         <f>C34/B34</f>
-        <v>0.94194685807832768</v>
+        <v>0.78579523989421995</v>
       </c>
       <c r="F34" s="17">
         <f>(C34+D34)/B34</f>
-        <v>3.3984636695630277</v>
+        <v>3.2423120513789194</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B35" s="11">
         <f>Demanda!D19</f>
@@ -3822,7 +4621,7 @@
       </c>
       <c r="C35" s="11">
         <f>Oferta!C7</f>
-        <v>9.35</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="D35" s="11">
         <f>Oferta!B20</f>
@@ -3830,16 +4629,16 @@
       </c>
       <c r="E35" s="17">
         <f>C35/B35</f>
-        <v>0.28382228171865775</v>
+        <v>0.23677152913428137</v>
       </c>
       <c r="F35" s="17">
         <f>(C35+D35)/B35</f>
-        <v>1.0240065081815191</v>
+        <v>0.97695575559714243</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B36" s="11">
         <f>Demanda!D20</f>
@@ -3847,7 +4646,7 @@
       </c>
       <c r="C36" s="11">
         <f>Oferta!C7</f>
-        <v>9.35</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="D36" s="11">
         <f>Oferta!B20</f>
@@ -3855,16 +4654,16 @@
       </c>
       <c r="E36" s="17">
         <f>C36/B36</f>
-        <v>0.12491649966599867</v>
+        <v>0.10420841683366736</v>
       </c>
       <c r="F36" s="17">
         <f>(C36+D36)/B36</f>
-        <v>0.45068804275217106</v>
+        <v>0.42997995991983967</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -3873,8 +4672,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3884,17 +4683,17 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B4" s="11">
         <f>Demanda!H14</f>
@@ -3903,7 +4702,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B6" s="22">
         <v>1</v>
@@ -4025,7 +4824,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
